--- a/modelle/calc.xlsx
+++ b/modelle/calc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\7_TU\Bachelor Elektrotechnik und Informationstechnik\Mechatronik und Instrumentierung\modelle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11651D8A-250E-4264-B90D-733EA15BBC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA778D2C-8BCE-4384-AF51-35435FBDA855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{91D3CBE4-807A-4057-826A-FD894EC27511}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
   <si>
     <t>n</t>
   </si>
@@ -78,6 +78,12 @@
   </si>
   <si>
     <t>mm</t>
+  </si>
+  <si>
+    <t>GT2 pulley</t>
+  </si>
+  <si>
+    <t>D_a</t>
   </si>
 </sst>
 </file>
@@ -1501,13 +1507,13 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
@@ -1530,7 +1536,7 @@
       </c>
       <c r="T11">
         <f>S11/S10</f>
-        <v>1.6190476190476191</v>
+        <v>1.4166666666666667</v>
       </c>
       <c r="V11" t="s">
         <v>7</v>
@@ -1540,7 +1546,7 @@
       </c>
       <c r="X11">
         <f>W11/W10</f>
-        <v>2</v>
+        <v>1.4166666666666667</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
@@ -1584,21 +1590,21 @@
         <v>2</v>
       </c>
       <c r="S13">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T13">
         <f>S13/S12</f>
-        <v>1.5789473684210527</v>
+        <v>1.7894736842105263</v>
       </c>
       <c r="V13">
         <v>2</v>
       </c>
       <c r="W13">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="X13">
         <f>W13/W12</f>
-        <v>1.5789473684210527</v>
+        <v>1.7894736842105263</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -1618,14 +1624,14 @@
       </c>
       <c r="T14">
         <f>T13*T11</f>
-        <v>2.5563909774436091</v>
+        <v>2.5350877192982457</v>
       </c>
       <c r="V14" t="s">
         <v>6</v>
       </c>
       <c r="X14">
         <f>X13*X11</f>
-        <v>3.1578947368421053</v>
+        <v>2.5350877192982457</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -1654,7 +1660,7 @@
         <v>12.623529411764707</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1667,7 +1673,7 @@
         <v>13.411764705882355</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1680,7 +1686,7 @@
         <v>14.203921568627452</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1693,7 +1699,7 @@
         <v>15.000000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1706,7 +1712,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1719,7 +1725,7 @@
         <v>16.603921568627452</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1732,7 +1738,7 @@
         <v>17.411764705882355</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1745,7 +1751,7 @@
         <v>18.223529411764709</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1762,7 +1768,7 @@
         <v>1.9583333333333333</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1785,7 +1791,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1798,7 +1804,7 @@
         <v>20.682352941176472</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1811,7 +1817,7 @@
         <v>21.509803921568629</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1824,7 +1830,7 @@
         <v>22.341176470588238</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1836,8 +1842,11 @@
         <f t="shared" si="2"/>
         <v>23.176470588235293</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="R29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1849,8 +1858,20 @@
         <f t="shared" si="2"/>
         <v>24.015686274509804</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="S30" t="s">
+        <v>0</v>
+      </c>
+      <c r="T30" t="s">
+        <v>3</v>
+      </c>
+      <c r="U30" t="s">
+        <v>2</v>
+      </c>
+      <c r="V30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1862,8 +1883,23 @@
         <f t="shared" si="2"/>
         <v>24.858823529411765</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="S31">
+        <v>10</v>
+      </c>
+      <c r="T31">
+        <f>1-1.25*PI()/(2*S31)</f>
+        <v>0.80365045915063793</v>
+      </c>
+      <c r="U31">
+        <f>S31*2*T31/PI()+1</f>
+        <v>6.1161977236758132</v>
+      </c>
+      <c r="V31">
+        <f>S31*2*T31/PI()+2*1</f>
+        <v>7.1161977236758132</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1875,8 +1911,23 @@
         <f t="shared" si="2"/>
         <v>25.705882352941174</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S32">
+        <v>11</v>
+      </c>
+      <c r="T32">
+        <f t="shared" ref="T32:T51" si="3">1-1.25*PI()/(2*S32)</f>
+        <v>0.82150041740967084</v>
+      </c>
+      <c r="U32">
+        <f t="shared" ref="U32:U51" si="4">S32*2*T32/PI()+1</f>
+        <v>6.7528174960433951</v>
+      </c>
+      <c r="V32">
+        <f>S32*2*T32/PI()+2*1</f>
+        <v>7.7528174960433951</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1888,8 +1939,27 @@
         <f t="shared" si="2"/>
         <v>26.556862745098041</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S33">
+        <v>12</v>
+      </c>
+      <c r="T33">
+        <f t="shared" si="3"/>
+        <v>0.83637538262553157</v>
+      </c>
+      <c r="U33">
+        <f t="shared" si="4"/>
+        <v>7.3894372684109761</v>
+      </c>
+      <c r="V33">
+        <f>S33*2*T33/PI()+2*1</f>
+        <v>8.3894372684109761</v>
+      </c>
+      <c r="W33">
+        <f>7.553+0.75</f>
+        <v>8.3030000000000008</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1901,8 +1971,23 @@
         <f t="shared" si="2"/>
         <v>27.411764705882355</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S34">
+        <v>13</v>
+      </c>
+      <c r="T34">
+        <f t="shared" si="3"/>
+        <v>0.84896189165433689</v>
+      </c>
+      <c r="U34">
+        <f t="shared" si="4"/>
+        <v>8.0260570407785572</v>
+      </c>
+      <c r="V34">
+        <f>S34*2*T34/PI()+2*1</f>
+        <v>9.0260570407785572</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1914,8 +1999,27 @@
         <f t="shared" si="2"/>
         <v>28.270588235294117</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="P35">
+        <f>1.38-0.75</f>
+        <v>0.62999999999999989</v>
+      </c>
+      <c r="S35">
+        <v>14</v>
+      </c>
+      <c r="T35">
+        <f t="shared" si="3"/>
+        <v>0.85975032796474138</v>
+      </c>
+      <c r="U35">
+        <f t="shared" si="4"/>
+        <v>8.6626768131461382</v>
+      </c>
+      <c r="V35">
+        <f>S35*2*T35/PI()+2*1</f>
+        <v>9.6626768131461382</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1927,8 +2031,23 @@
         <f t="shared" si="2"/>
         <v>29.133333333333333</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S36">
+        <v>15</v>
+      </c>
+      <c r="T36">
+        <f t="shared" si="3"/>
+        <v>0.86910030610042532</v>
+      </c>
+      <c r="U36">
+        <f t="shared" si="4"/>
+        <v>9.2992965855137211</v>
+      </c>
+      <c r="V36">
+        <f>S36*2*T36/PI()+2*1</f>
+        <v>10.299296585513721</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1940,8 +2059,23 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S37">
+        <v>16</v>
+      </c>
+      <c r="T37">
+        <f t="shared" si="3"/>
+        <v>0.87728153696914868</v>
+      </c>
+      <c r="U37">
+        <f t="shared" si="4"/>
+        <v>9.9359163578813021</v>
+      </c>
+      <c r="V37">
+        <f>S37*2*T37/PI()+2*1</f>
+        <v>10.935916357881302</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1950,11 +2084,26 @@
         <v>1.2597170542335543</v>
       </c>
       <c r="C38">
-        <f t="shared" ref="C38:C56" si="3">B38*2*A38/PI()+2</f>
+        <f t="shared" ref="C38:C56" si="5">B38*2*A38/PI()+2</f>
         <v>30.870588235294118</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S38">
+        <v>17</v>
+      </c>
+      <c r="T38">
+        <f t="shared" si="3"/>
+        <v>0.88450027008861054</v>
+      </c>
+      <c r="U38">
+        <f t="shared" si="4"/>
+        <v>10.572536130248883</v>
+      </c>
+      <c r="V38">
+        <f>S38*2*T38/PI()+2*1</f>
+        <v>11.572536130248883</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1963,11 +2112,26 @@
         <v>1.2627970470311913</v>
       </c>
       <c r="C39">
+        <f t="shared" si="5"/>
+        <v>31.745098039215684</v>
+      </c>
+      <c r="S39">
+        <v>18</v>
+      </c>
+      <c r="T39">
         <f t="shared" si="3"/>
-        <v>31.745098039215684</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.89091692175035442</v>
+      </c>
+      <c r="U39">
+        <f t="shared" si="4"/>
+        <v>11.209155902616464</v>
+      </c>
+      <c r="V39">
+        <f>S39*2*T39/PI()+2*1</f>
+        <v>12.209155902616464</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1976,11 +2140,26 @@
         <v>1.2658770398288284</v>
       </c>
       <c r="C40">
+        <f t="shared" si="5"/>
+        <v>32.623529411764707</v>
+      </c>
+      <c r="S40">
+        <v>19</v>
+      </c>
+      <c r="T40">
         <f t="shared" si="3"/>
-        <v>32.623529411764707</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.89665813639507264</v>
+      </c>
+      <c r="U40">
+        <f t="shared" si="4"/>
+        <v>11.845775674984045</v>
+      </c>
+      <c r="V40">
+        <f>S40*2*T40/PI()+2*1</f>
+        <v>12.845775674984045</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1989,11 +2168,26 @@
         <v>1.2689570326264654</v>
       </c>
       <c r="C41">
+        <f t="shared" si="5"/>
+        <v>33.505882352941171</v>
+      </c>
+      <c r="S41">
+        <v>20</v>
+      </c>
+      <c r="T41">
         <f t="shared" si="3"/>
-        <v>33.505882352941171</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.90182522957531897</v>
+      </c>
+      <c r="U41">
+        <f t="shared" si="4"/>
+        <v>12.482395447351626</v>
+      </c>
+      <c r="V41">
+        <f>S41*2*T41/PI()+2*1</f>
+        <v>13.482395447351626</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>40</v>
       </c>
@@ -2002,11 +2196,26 @@
         <v>1.2720370254241025</v>
       </c>
       <c r="C42">
+        <f t="shared" si="5"/>
+        <v>34.392156862745097</v>
+      </c>
+      <c r="S42">
+        <v>21</v>
+      </c>
+      <c r="T42">
         <f t="shared" si="3"/>
-        <v>34.392156862745097</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.90650021864316088</v>
+      </c>
+      <c r="U42">
+        <f t="shared" si="4"/>
+        <v>13.119015219719209</v>
+      </c>
+      <c r="V42">
+        <f>S42*2*T42/PI()+2*1</f>
+        <v>14.119015219719209</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>41</v>
       </c>
@@ -2015,11 +2224,26 @@
         <v>1.2751170182217395</v>
       </c>
       <c r="C43">
+        <f t="shared" si="5"/>
+        <v>35.28235294117647</v>
+      </c>
+      <c r="S43">
+        <v>22</v>
+      </c>
+      <c r="T43">
         <f t="shared" si="3"/>
-        <v>35.28235294117647</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.91075020870483536</v>
+      </c>
+      <c r="U43">
+        <f t="shared" si="4"/>
+        <v>13.75563499208679</v>
+      </c>
+      <c r="V43">
+        <f>S43*2*T43/PI()+2*1</f>
+        <v>14.75563499208679</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>42</v>
       </c>
@@ -2028,11 +2252,26 @@
         <v>1.2781970110193765</v>
       </c>
       <c r="C44">
+        <f t="shared" si="5"/>
+        <v>36.176470588235297</v>
+      </c>
+      <c r="S44">
+        <v>23</v>
+      </c>
+      <c r="T44">
         <f t="shared" si="3"/>
-        <v>36.176470588235297</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.91463063441332082</v>
+      </c>
+      <c r="U44">
+        <f t="shared" si="4"/>
+        <v>14.392254764454371</v>
+      </c>
+      <c r="V44">
+        <f>S44*2*T44/PI()+2*1</f>
+        <v>15.392254764454371</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>43</v>
       </c>
@@ -2041,11 +2280,26 @@
         <v>1.2812770038170136</v>
       </c>
       <c r="C45">
+        <f t="shared" si="5"/>
+        <v>37.074509803921572</v>
+      </c>
+      <c r="S45">
+        <v>24</v>
+      </c>
+      <c r="T45">
         <f t="shared" si="3"/>
-        <v>37.074509803921572</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.91818769131276579</v>
+      </c>
+      <c r="U45">
+        <f t="shared" si="4"/>
+        <v>15.028874536821952</v>
+      </c>
+      <c r="V45">
+        <f>S45*2*T45/PI()+2*1</f>
+        <v>16.028874536821952</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>44</v>
       </c>
@@ -2054,11 +2308,26 @@
         <v>1.2843569966146506</v>
       </c>
       <c r="C46">
+        <f t="shared" si="5"/>
+        <v>37.976470588235294</v>
+      </c>
+      <c r="S46">
+        <v>25</v>
+      </c>
+      <c r="T46">
         <f t="shared" si="3"/>
-        <v>37.976470588235294</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.92146018366025517</v>
+      </c>
+      <c r="U46">
+        <f t="shared" si="4"/>
+        <v>15.665494309189533</v>
+      </c>
+      <c r="V46">
+        <f>S46*2*T46/PI()+2*1</f>
+        <v>16.665494309189533</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>45</v>
       </c>
@@ -2067,11 +2336,26 @@
         <v>1.2874369894122877</v>
       </c>
       <c r="C47">
+        <f t="shared" si="5"/>
+        <v>38.882352941176471</v>
+      </c>
+      <c r="S47">
+        <v>26</v>
+      </c>
+      <c r="T47">
         <f t="shared" si="3"/>
-        <v>38.882352941176471</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.92448094582716844</v>
+      </c>
+      <c r="U47">
+        <f t="shared" si="4"/>
+        <v>16.302114081557114</v>
+      </c>
+      <c r="V47">
+        <f>S47*2*T47/PI()+2*1</f>
+        <v>17.302114081557114</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>46</v>
       </c>
@@ -2080,11 +2364,26 @@
         <v>1.2905169822099247</v>
       </c>
       <c r="C48">
+        <f t="shared" si="5"/>
+        <v>39.792156862745095</v>
+      </c>
+      <c r="S48">
+        <v>27</v>
+      </c>
+      <c r="T48">
         <f t="shared" si="3"/>
-        <v>39.792156862745095</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.92727794783356965</v>
+      </c>
+      <c r="U48">
+        <f t="shared" si="4"/>
+        <v>16.938733853924695</v>
+      </c>
+      <c r="V48">
+        <f>S48*2*T48/PI()+2*1</f>
+        <v>17.938733853924695</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>47</v>
       </c>
@@ -2093,11 +2392,26 @@
         <v>1.2935969750075618</v>
       </c>
       <c r="C49">
+        <f t="shared" si="5"/>
+        <v>40.705882352941174</v>
+      </c>
+      <c r="S49">
+        <v>28</v>
+      </c>
+      <c r="T49">
         <f t="shared" si="3"/>
-        <v>40.705882352941174</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.92987516398237069</v>
+      </c>
+      <c r="U49">
+        <f t="shared" si="4"/>
+        <v>17.575353626292276</v>
+      </c>
+      <c r="V49">
+        <f>S49*2*T49/PI()+2*1</f>
+        <v>18.575353626292276</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>48</v>
       </c>
@@ -2106,11 +2420,26 @@
         <v>1.2966769678051988</v>
       </c>
       <c r="C50">
+        <f t="shared" si="5"/>
+        <v>41.6235294117647</v>
+      </c>
+      <c r="S50">
+        <v>29</v>
+      </c>
+      <c r="T50">
         <f t="shared" si="3"/>
-        <v>41.6235294117647</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.93229326177608207</v>
+      </c>
+      <c r="U50">
+        <f t="shared" si="4"/>
+        <v>18.211973398659861</v>
+      </c>
+      <c r="V50">
+        <f>S50*2*T50/PI()+2*1</f>
+        <v>19.211973398659861</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>49</v>
       </c>
@@ -2119,11 +2448,26 @@
         <v>1.2997569606028359</v>
       </c>
       <c r="C51">
+        <f t="shared" si="5"/>
+        <v>42.545098039215681</v>
+      </c>
+      <c r="S51">
+        <v>30</v>
+      </c>
+      <c r="T51">
         <f t="shared" si="3"/>
-        <v>42.545098039215681</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.93455015305021261</v>
+      </c>
+      <c r="U51">
+        <f t="shared" si="4"/>
+        <v>18.848593171027442</v>
+      </c>
+      <c r="V51">
+        <f>S51*2*T51/PI()+2*1</f>
+        <v>19.848593171027442</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>50</v>
       </c>
@@ -2132,11 +2476,11 @@
         <v>1.3028369534004729</v>
       </c>
       <c r="C52">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>43.470588235294116</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>51</v>
       </c>
@@ -2145,11 +2489,11 @@
         <v>1.3059169461981099</v>
       </c>
       <c r="C53">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>44.4</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>52</v>
       </c>
@@ -2158,11 +2502,11 @@
         <v>1.308996938995747</v>
       </c>
       <c r="C54">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>45.333333333333321</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>53</v>
       </c>
@@ -2171,11 +2515,11 @@
         <v>1.312076931793384</v>
       </c>
       <c r="C55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46.270588235294113</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>54</v>
       </c>
@@ -2184,7 +2528,7 @@
         <v>1.3151569245910211</v>
       </c>
       <c r="C56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>47.211764705882345</v>
       </c>
     </row>

--- a/modelle/calc.xlsx
+++ b/modelle/calc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\7_TU\Bachelor Elektrotechnik und Informationstechnik\Mechatronik und Instrumentierung\modelle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA778D2C-8BCE-4384-AF51-35435FBDA855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FC4DA7-EA10-4153-9323-500CE7937C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{91D3CBE4-807A-4057-826A-FD894EC27511}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{91D3CBE4-807A-4057-826A-FD894EC27511}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -1895,7 +1895,7 @@
         <v>6.1161977236758132</v>
       </c>
       <c r="V31">
-        <f>S31*2*T31/PI()+2*1</f>
+        <f t="shared" ref="V31:V51" si="3">S31*2*T31/PI()+2*1</f>
         <v>7.1161977236758132</v>
       </c>
     </row>
@@ -1915,15 +1915,15 @@
         <v>11</v>
       </c>
       <c r="T32">
-        <f t="shared" ref="T32:T51" si="3">1-1.25*PI()/(2*S32)</f>
+        <f t="shared" ref="T32:T51" si="4">1-1.25*PI()/(2*S32)</f>
         <v>0.82150041740967084</v>
       </c>
       <c r="U32">
-        <f t="shared" ref="U32:U51" si="4">S32*2*T32/PI()+1</f>
+        <f t="shared" ref="U32:U51" si="5">S32*2*T32/PI()+1</f>
         <v>6.7528174960433951</v>
       </c>
       <c r="V32">
-        <f>S32*2*T32/PI()+2*1</f>
+        <f t="shared" si="3"/>
         <v>7.7528174960433951</v>
       </c>
     </row>
@@ -1943,15 +1943,15 @@
         <v>12</v>
       </c>
       <c r="T33">
+        <f t="shared" si="4"/>
+        <v>0.83637538262553157</v>
+      </c>
+      <c r="U33">
+        <f t="shared" si="5"/>
+        <v>7.3894372684109761</v>
+      </c>
+      <c r="V33">
         <f t="shared" si="3"/>
-        <v>0.83637538262553157</v>
-      </c>
-      <c r="U33">
-        <f t="shared" si="4"/>
-        <v>7.3894372684109761</v>
-      </c>
-      <c r="V33">
-        <f>S33*2*T33/PI()+2*1</f>
         <v>8.3894372684109761</v>
       </c>
       <c r="W33">
@@ -1975,15 +1975,15 @@
         <v>13</v>
       </c>
       <c r="T34">
+        <f t="shared" si="4"/>
+        <v>0.84896189165433689</v>
+      </c>
+      <c r="U34">
+        <f t="shared" si="5"/>
+        <v>8.0260570407785572</v>
+      </c>
+      <c r="V34">
         <f t="shared" si="3"/>
-        <v>0.84896189165433689</v>
-      </c>
-      <c r="U34">
-        <f t="shared" si="4"/>
-        <v>8.0260570407785572</v>
-      </c>
-      <c r="V34">
-        <f>S34*2*T34/PI()+2*1</f>
         <v>9.0260570407785572</v>
       </c>
     </row>
@@ -2007,15 +2007,15 @@
         <v>14</v>
       </c>
       <c r="T35">
+        <f t="shared" si="4"/>
+        <v>0.85975032796474138</v>
+      </c>
+      <c r="U35">
+        <f t="shared" si="5"/>
+        <v>8.6626768131461382</v>
+      </c>
+      <c r="V35">
         <f t="shared" si="3"/>
-        <v>0.85975032796474138</v>
-      </c>
-      <c r="U35">
-        <f t="shared" si="4"/>
-        <v>8.6626768131461382</v>
-      </c>
-      <c r="V35">
-        <f>S35*2*T35/PI()+2*1</f>
         <v>9.6626768131461382</v>
       </c>
     </row>
@@ -2035,15 +2035,15 @@
         <v>15</v>
       </c>
       <c r="T36">
+        <f t="shared" si="4"/>
+        <v>0.86910030610042532</v>
+      </c>
+      <c r="U36">
+        <f t="shared" si="5"/>
+        <v>9.2992965855137211</v>
+      </c>
+      <c r="V36">
         <f t="shared" si="3"/>
-        <v>0.86910030610042532</v>
-      </c>
-      <c r="U36">
-        <f t="shared" si="4"/>
-        <v>9.2992965855137211</v>
-      </c>
-      <c r="V36">
-        <f>S36*2*T36/PI()+2*1</f>
         <v>10.299296585513721</v>
       </c>
     </row>
@@ -2063,15 +2063,15 @@
         <v>16</v>
       </c>
       <c r="T37">
+        <f t="shared" si="4"/>
+        <v>0.87728153696914868</v>
+      </c>
+      <c r="U37">
+        <f t="shared" si="5"/>
+        <v>9.9359163578813021</v>
+      </c>
+      <c r="V37">
         <f t="shared" si="3"/>
-        <v>0.87728153696914868</v>
-      </c>
-      <c r="U37">
-        <f t="shared" si="4"/>
-        <v>9.9359163578813021</v>
-      </c>
-      <c r="V37">
-        <f>S37*2*T37/PI()+2*1</f>
         <v>10.935916357881302</v>
       </c>
     </row>
@@ -2084,22 +2084,22 @@
         <v>1.2597170542335543</v>
       </c>
       <c r="C38">
-        <f t="shared" ref="C38:C56" si="5">B38*2*A38/PI()+2</f>
+        <f t="shared" ref="C38:C56" si="6">B38*2*A38/PI()+2</f>
         <v>30.870588235294118</v>
       </c>
       <c r="S38">
         <v>17</v>
       </c>
       <c r="T38">
+        <f t="shared" si="4"/>
+        <v>0.88450027008861054</v>
+      </c>
+      <c r="U38">
+        <f t="shared" si="5"/>
+        <v>10.572536130248883</v>
+      </c>
+      <c r="V38">
         <f t="shared" si="3"/>
-        <v>0.88450027008861054</v>
-      </c>
-      <c r="U38">
-        <f t="shared" si="4"/>
-        <v>10.572536130248883</v>
-      </c>
-      <c r="V38">
-        <f>S38*2*T38/PI()+2*1</f>
         <v>11.572536130248883</v>
       </c>
     </row>
@@ -2112,22 +2112,22 @@
         <v>1.2627970470311913</v>
       </c>
       <c r="C39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>31.745098039215684</v>
       </c>
       <c r="S39">
         <v>18</v>
       </c>
       <c r="T39">
+        <f t="shared" si="4"/>
+        <v>0.89091692175035442</v>
+      </c>
+      <c r="U39">
+        <f t="shared" si="5"/>
+        <v>11.209155902616464</v>
+      </c>
+      <c r="V39">
         <f t="shared" si="3"/>
-        <v>0.89091692175035442</v>
-      </c>
-      <c r="U39">
-        <f t="shared" si="4"/>
-        <v>11.209155902616464</v>
-      </c>
-      <c r="V39">
-        <f>S39*2*T39/PI()+2*1</f>
         <v>12.209155902616464</v>
       </c>
     </row>
@@ -2140,22 +2140,22 @@
         <v>1.2658770398288284</v>
       </c>
       <c r="C40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>32.623529411764707</v>
       </c>
       <c r="S40">
         <v>19</v>
       </c>
       <c r="T40">
+        <f t="shared" si="4"/>
+        <v>0.89665813639507264</v>
+      </c>
+      <c r="U40">
+        <f t="shared" si="5"/>
+        <v>11.845775674984045</v>
+      </c>
+      <c r="V40">
         <f t="shared" si="3"/>
-        <v>0.89665813639507264</v>
-      </c>
-      <c r="U40">
-        <f t="shared" si="4"/>
-        <v>11.845775674984045</v>
-      </c>
-      <c r="V40">
-        <f>S40*2*T40/PI()+2*1</f>
         <v>12.845775674984045</v>
       </c>
     </row>
@@ -2168,22 +2168,22 @@
         <v>1.2689570326264654</v>
       </c>
       <c r="C41">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>33.505882352941171</v>
       </c>
       <c r="S41">
         <v>20</v>
       </c>
       <c r="T41">
+        <f t="shared" si="4"/>
+        <v>0.90182522957531897</v>
+      </c>
+      <c r="U41">
+        <f t="shared" si="5"/>
+        <v>12.482395447351626</v>
+      </c>
+      <c r="V41">
         <f t="shared" si="3"/>
-        <v>0.90182522957531897</v>
-      </c>
-      <c r="U41">
-        <f t="shared" si="4"/>
-        <v>12.482395447351626</v>
-      </c>
-      <c r="V41">
-        <f>S41*2*T41/PI()+2*1</f>
         <v>13.482395447351626</v>
       </c>
     </row>
@@ -2196,22 +2196,22 @@
         <v>1.2720370254241025</v>
       </c>
       <c r="C42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>34.392156862745097</v>
       </c>
       <c r="S42">
         <v>21</v>
       </c>
       <c r="T42">
+        <f t="shared" si="4"/>
+        <v>0.90650021864316088</v>
+      </c>
+      <c r="U42">
+        <f t="shared" si="5"/>
+        <v>13.119015219719209</v>
+      </c>
+      <c r="V42">
         <f t="shared" si="3"/>
-        <v>0.90650021864316088</v>
-      </c>
-      <c r="U42">
-        <f t="shared" si="4"/>
-        <v>13.119015219719209</v>
-      </c>
-      <c r="V42">
-        <f>S42*2*T42/PI()+2*1</f>
         <v>14.119015219719209</v>
       </c>
     </row>
@@ -2224,22 +2224,22 @@
         <v>1.2751170182217395</v>
       </c>
       <c r="C43">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>35.28235294117647</v>
       </c>
       <c r="S43">
         <v>22</v>
       </c>
       <c r="T43">
+        <f t="shared" si="4"/>
+        <v>0.91075020870483536</v>
+      </c>
+      <c r="U43">
+        <f t="shared" si="5"/>
+        <v>13.75563499208679</v>
+      </c>
+      <c r="V43">
         <f t="shared" si="3"/>
-        <v>0.91075020870483536</v>
-      </c>
-      <c r="U43">
-        <f t="shared" si="4"/>
-        <v>13.75563499208679</v>
-      </c>
-      <c r="V43">
-        <f>S43*2*T43/PI()+2*1</f>
         <v>14.75563499208679</v>
       </c>
     </row>
@@ -2252,22 +2252,22 @@
         <v>1.2781970110193765</v>
       </c>
       <c r="C44">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>36.176470588235297</v>
       </c>
       <c r="S44">
         <v>23</v>
       </c>
       <c r="T44">
+        <f t="shared" si="4"/>
+        <v>0.91463063441332082</v>
+      </c>
+      <c r="U44">
+        <f t="shared" si="5"/>
+        <v>14.392254764454371</v>
+      </c>
+      <c r="V44">
         <f t="shared" si="3"/>
-        <v>0.91463063441332082</v>
-      </c>
-      <c r="U44">
-        <f t="shared" si="4"/>
-        <v>14.392254764454371</v>
-      </c>
-      <c r="V44">
-        <f>S44*2*T44/PI()+2*1</f>
         <v>15.392254764454371</v>
       </c>
     </row>
@@ -2280,22 +2280,22 @@
         <v>1.2812770038170136</v>
       </c>
       <c r="C45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>37.074509803921572</v>
       </c>
       <c r="S45">
         <v>24</v>
       </c>
       <c r="T45">
+        <f t="shared" si="4"/>
+        <v>0.91818769131276579</v>
+      </c>
+      <c r="U45">
+        <f t="shared" si="5"/>
+        <v>15.028874536821952</v>
+      </c>
+      <c r="V45">
         <f t="shared" si="3"/>
-        <v>0.91818769131276579</v>
-      </c>
-      <c r="U45">
-        <f t="shared" si="4"/>
-        <v>15.028874536821952</v>
-      </c>
-      <c r="V45">
-        <f>S45*2*T45/PI()+2*1</f>
         <v>16.028874536821952</v>
       </c>
     </row>
@@ -2308,22 +2308,22 @@
         <v>1.2843569966146506</v>
       </c>
       <c r="C46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>37.976470588235294</v>
       </c>
       <c r="S46">
         <v>25</v>
       </c>
       <c r="T46">
+        <f t="shared" si="4"/>
+        <v>0.92146018366025517</v>
+      </c>
+      <c r="U46">
+        <f t="shared" si="5"/>
+        <v>15.665494309189533</v>
+      </c>
+      <c r="V46">
         <f t="shared" si="3"/>
-        <v>0.92146018366025517</v>
-      </c>
-      <c r="U46">
-        <f t="shared" si="4"/>
-        <v>15.665494309189533</v>
-      </c>
-      <c r="V46">
-        <f>S46*2*T46/PI()+2*1</f>
         <v>16.665494309189533</v>
       </c>
     </row>
@@ -2336,22 +2336,22 @@
         <v>1.2874369894122877</v>
       </c>
       <c r="C47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>38.882352941176471</v>
       </c>
       <c r="S47">
         <v>26</v>
       </c>
       <c r="T47">
+        <f t="shared" si="4"/>
+        <v>0.92448094582716844</v>
+      </c>
+      <c r="U47">
+        <f t="shared" si="5"/>
+        <v>16.302114081557114</v>
+      </c>
+      <c r="V47">
         <f t="shared" si="3"/>
-        <v>0.92448094582716844</v>
-      </c>
-      <c r="U47">
-        <f t="shared" si="4"/>
-        <v>16.302114081557114</v>
-      </c>
-      <c r="V47">
-        <f>S47*2*T47/PI()+2*1</f>
         <v>17.302114081557114</v>
       </c>
     </row>
@@ -2364,22 +2364,22 @@
         <v>1.2905169822099247</v>
       </c>
       <c r="C48">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>39.792156862745095</v>
       </c>
       <c r="S48">
         <v>27</v>
       </c>
       <c r="T48">
+        <f t="shared" si="4"/>
+        <v>0.92727794783356965</v>
+      </c>
+      <c r="U48">
+        <f t="shared" si="5"/>
+        <v>16.938733853924695</v>
+      </c>
+      <c r="V48">
         <f t="shared" si="3"/>
-        <v>0.92727794783356965</v>
-      </c>
-      <c r="U48">
-        <f t="shared" si="4"/>
-        <v>16.938733853924695</v>
-      </c>
-      <c r="V48">
-        <f>S48*2*T48/PI()+2*1</f>
         <v>17.938733853924695</v>
       </c>
     </row>
@@ -2392,22 +2392,22 @@
         <v>1.2935969750075618</v>
       </c>
       <c r="C49">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>40.705882352941174</v>
       </c>
       <c r="S49">
         <v>28</v>
       </c>
       <c r="T49">
+        <f t="shared" si="4"/>
+        <v>0.92987516398237069</v>
+      </c>
+      <c r="U49">
+        <f t="shared" si="5"/>
+        <v>17.575353626292276</v>
+      </c>
+      <c r="V49">
         <f t="shared" si="3"/>
-        <v>0.92987516398237069</v>
-      </c>
-      <c r="U49">
-        <f t="shared" si="4"/>
-        <v>17.575353626292276</v>
-      </c>
-      <c r="V49">
-        <f>S49*2*T49/PI()+2*1</f>
         <v>18.575353626292276</v>
       </c>
     </row>
@@ -2420,22 +2420,22 @@
         <v>1.2966769678051988</v>
       </c>
       <c r="C50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>41.6235294117647</v>
       </c>
       <c r="S50">
         <v>29</v>
       </c>
       <c r="T50">
+        <f t="shared" si="4"/>
+        <v>0.93229326177608207</v>
+      </c>
+      <c r="U50">
+        <f t="shared" si="5"/>
+        <v>18.211973398659861</v>
+      </c>
+      <c r="V50">
         <f t="shared" si="3"/>
-        <v>0.93229326177608207</v>
-      </c>
-      <c r="U50">
-        <f t="shared" si="4"/>
-        <v>18.211973398659861</v>
-      </c>
-      <c r="V50">
-        <f>S50*2*T50/PI()+2*1</f>
         <v>19.211973398659861</v>
       </c>
     </row>
@@ -2448,22 +2448,22 @@
         <v>1.2997569606028359</v>
       </c>
       <c r="C51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>42.545098039215681</v>
       </c>
       <c r="S51">
         <v>30</v>
       </c>
       <c r="T51">
+        <f t="shared" si="4"/>
+        <v>0.93455015305021261</v>
+      </c>
+      <c r="U51">
+        <f t="shared" si="5"/>
+        <v>18.848593171027442</v>
+      </c>
+      <c r="V51">
         <f t="shared" si="3"/>
-        <v>0.93455015305021261</v>
-      </c>
-      <c r="U51">
-        <f t="shared" si="4"/>
-        <v>18.848593171027442</v>
-      </c>
-      <c r="V51">
-        <f>S51*2*T51/PI()+2*1</f>
         <v>19.848593171027442</v>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
         <v>1.3028369534004729</v>
       </c>
       <c r="C52">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>43.470588235294116</v>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
         <v>1.3059169461981099</v>
       </c>
       <c r="C53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>44.4</v>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
         <v>1.308996938995747</v>
       </c>
       <c r="C54">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>45.333333333333321</v>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>1.312076931793384</v>
       </c>
       <c r="C55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>46.270588235294113</v>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
         <v>1.3151569245910211</v>
       </c>
       <c r="C56">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>47.211764705882345</v>
       </c>
     </row>

--- a/modelle/calc.xlsx
+++ b/modelle/calc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\7_TU\Bachelor Elektrotechnik und Informationstechnik\Mechatronik und Instrumentierung\modelle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FC4DA7-EA10-4153-9323-500CE7937C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CF43BA-740B-42A6-BA9F-A6B248BA7ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{91D3CBE4-807A-4057-826A-FD894EC27511}"/>
   </bookViews>
